--- a/Config/Datas/Tables/z_战斗界面_CombatUiSetConfig.xlsx
+++ b/Config/Datas/Tables/z_战斗界面_CombatUiSetConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbCombatUiSet" sheetId="1" r:id="Rd70cb7aecdbc4f50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbCombatUiSet" sheetId="1" r:id="Rbc7bc5425b7c47db"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -46,8 +46,36 @@
       <x:color rgb="FF334E68"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF243B53"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF486581"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF334E68"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="14">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -67,6 +95,46 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFEEF5FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F8FB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F8FB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -95,7 +163,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="67">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -132,6 +200,113 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -346,6 +521,17 @@
     <x:col min="8" max="8" width="13" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="13" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="31" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="20" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="20" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="20" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="20" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="20" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="42" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -379,6 +565,39 @@
       <x:c r="J1" s="7" t="str">
         <x:v>restartText</x:v>
       </x:c>
+      <x:c r="K1" s="19" t="str">
+        <x:v>upgradeCardPrefabResourceId</x:v>
+      </x:c>
+      <x:c r="L1" s="19" t="str">
+        <x:v>fontResourceId</x:v>
+      </x:c>
+      <x:c r="M1" s="48" t="str">
+        <x:v>healthFormat</x:v>
+      </x:c>
+      <x:c r="N1" s="48" t="str">
+        <x:v>timerFormat</x:v>
+      </x:c>
+      <x:c r="O1" s="48" t="str">
+        <x:v>levelFormat</x:v>
+      </x:c>
+      <x:c r="P1" s="48" t="str">
+        <x:v>experienceFormat</x:v>
+      </x:c>
+      <x:c r="Q1" s="48" t="str">
+        <x:v>killsFormat</x:v>
+      </x:c>
+      <x:c r="R1" s="48" t="str">
+        <x:v>waveFormat</x:v>
+      </x:c>
+      <x:c r="S1" s="48" t="str">
+        <x:v>bossHealthFormat</x:v>
+      </x:c>
+      <x:c r="T1" s="48" t="str">
+        <x:v>settlementStatsFormat</x:v>
+      </x:c>
+      <x:c r="U1" s="48" t="str">
+        <x:v>rankFormat</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="9" t="str">
@@ -409,6 +628,39 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="J2" s="9" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="K2" s="25" t="str">
+        <x:v>int#ref=TbResource</x:v>
+      </x:c>
+      <x:c r="L2" s="25" t="str">
+        <x:v>int#ref=TbResource</x:v>
+      </x:c>
+      <x:c r="M2" s="54" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="N2" s="54" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="O2" s="54" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="P2" s="54" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="Q2" s="54" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="R2" s="54" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="S2" s="54" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="T2" s="54" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="U2" s="54" t="str">
         <x:v>string</x:v>
       </x:c>
     </x:row>
@@ -425,6 +677,17 @@
       <x:c r="H3" s="11"/>
       <x:c r="I3" s="11"/>
       <x:c r="J3" s="11"/>
+      <x:c r="K3" s="31"/>
+      <x:c r="L3" s="31"/>
+      <x:c r="M3" s="60"/>
+      <x:c r="N3" s="60"/>
+      <x:c r="O3" s="60"/>
+      <x:c r="P3" s="60"/>
+      <x:c r="Q3" s="60"/>
+      <x:c r="R3" s="60"/>
+      <x:c r="S3" s="60"/>
+      <x:c r="T3" s="60"/>
+      <x:c r="U3" s="60"/>
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="13" t="str">
@@ -457,18 +720,102 @@
       <x:c r="J4" s="13" t="str">
         <x:v>重开按钮文本</x:v>
       </x:c>
+      <x:c r="K4" s="37" t="str">
+        <x:v>升级卡片Prefab资源</x:v>
+      </x:c>
+      <x:c r="L4" s="37" t="str">
+        <x:v>界面字体资源</x:v>
+      </x:c>
+      <x:c r="M4" s="66" t="str">
+        <x:v>生命显示格式</x:v>
+      </x:c>
+      <x:c r="N4" s="66" t="str">
+        <x:v>计时显示格式</x:v>
+      </x:c>
+      <x:c r="O4" s="66" t="str">
+        <x:v>等级显示格式</x:v>
+      </x:c>
+      <x:c r="P4" s="66" t="str">
+        <x:v>经验显示格式</x:v>
+      </x:c>
+      <x:c r="Q4" s="66" t="str">
+        <x:v>击杀显示格式</x:v>
+      </x:c>
+      <x:c r="R4" s="66" t="str">
+        <x:v>波次显示格式</x:v>
+      </x:c>
+      <x:c r="S4" s="66" t="str">
+        <x:v>Boss生命显示格式</x:v>
+      </x:c>
+      <x:c r="T4" s="66" t="str">
+        <x:v>结算统计格式</x:v>
+      </x:c>
+      <x:c r="U4" s="66" t="str">
+        <x:v>升级卡等级格式</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="5"/>
-      <x:c r="B5" s="5"/>
-      <x:c r="C5" s="5"/>
-      <x:c r="D5" s="5"/>
-      <x:c r="E5" s="5"/>
-      <x:c r="F5" s="5"/>
-      <x:c r="G5" s="5"/>
-      <x:c r="H5" s="5"/>
-      <x:c r="I5" s="5"/>
-      <x:c r="J5" s="5"/>
+      <x:c r="B5" s="5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="n">
+        <x:v>960001</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="n">
+        <x:v>960002</x:v>
+      </x:c>
+      <x:c r="E5" s="5" t="n">
+        <x:v>960003</x:v>
+      </x:c>
+      <x:c r="F5" s="5" t="n">
+        <x:v>960005</x:v>
+      </x:c>
+      <x:c r="G5" s="5" t="str">
+        <x:v>等级提升</x:v>
+      </x:c>
+      <x:c r="H5" s="5" t="str">
+        <x:v>胜利</x:v>
+      </x:c>
+      <x:c r="I5" s="5" t="str">
+        <x:v>失败</x:v>
+      </x:c>
+      <x:c r="J5" s="5" t="str">
+        <x:v>重新开始</x:v>
+      </x:c>
+      <x:c r="K5" s="42" t="n">
+        <x:v>960004</x:v>
+      </x:c>
+      <x:c r="L5" s="42" t="n">
+        <x:v>970001</x:v>
+      </x:c>
+      <x:c r="M5" s="42" t="str">
+        <x:v>生命 {0:0}/{1:0}</x:v>
+      </x:c>
+      <x:c r="N5" s="42" t="str">
+        <x:v>{0:00}:{1:00}</x:v>
+      </x:c>
+      <x:c r="O5" s="42" t="str">
+        <x:v>等级 {0}</x:v>
+      </x:c>
+      <x:c r="P5" s="42" t="str">
+        <x:v>经验 {0}/{1}</x:v>
+      </x:c>
+      <x:c r="Q5" s="42" t="str">
+        <x:v>击杀 {0}</x:v>
+      </x:c>
+      <x:c r="R5" s="42" t="str">
+        <x:v>波次 {0}</x:v>
+      </x:c>
+      <x:c r="S5" s="42" t="str">
+        <x:v>{0:0}/{1:0}</x:v>
+      </x:c>
+      <x:c r="T5" s="42" t="str">
+        <x:v>存活 {0:00}:{1:00}  击杀 {2}  等级 {3}</x:v>
+      </x:c>
+      <x:c r="U5" s="42" t="str">
+        <x:v>等级 {0}/{1}</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
